--- a/RoadMap.xlsx
+++ b/RoadMap.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFD2A0D-6A28-49F2-8D0F-F23F2C21C111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FAED4B-EBF9-4A11-A641-9E22B52D3D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Задачи" sheetId="1" r:id="rId1"/>
     <sheet name="Идеи" sheetId="2" r:id="rId2"/>
+    <sheet name="ЗИК" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Загрузка данных в виде DirHalfBars</t>
   </si>
@@ -62,6 +63,69 @@
   </si>
   <si>
     <t>2. Торговать лимитками, где в среду передавать результат его прошлой лимитки</t>
+  </si>
+  <si>
+    <t>PTA</t>
+  </si>
+  <si>
+    <t>LTA</t>
+  </si>
+  <si>
+    <t>OGTA</t>
+  </si>
+  <si>
+    <t>PSTA</t>
+  </si>
+  <si>
+    <t>STACA</t>
+  </si>
+  <si>
+    <t>STAML</t>
+  </si>
+  <si>
+    <t>STARL</t>
+  </si>
+  <si>
+    <t>STADL</t>
+  </si>
+  <si>
+    <t>Универсальный бот по индикатору полезности вариантов действия в DC</t>
+  </si>
+  <si>
+    <t>UpTrust и Spring уровней</t>
+  </si>
+  <si>
+    <t>Зоны по объем спреду</t>
+  </si>
+  <si>
+    <t>Последний бар с большим объемом</t>
+  </si>
+  <si>
+    <t>Завершение обновления экстремумов</t>
+  </si>
+  <si>
+    <t>Зоны по фракталам</t>
+  </si>
+  <si>
+    <t>Анализ зигзага</t>
+  </si>
+  <si>
+    <t>Взвешенные версии STAML2</t>
+  </si>
+  <si>
+    <t>STA2</t>
+  </si>
+  <si>
+    <t>ЦАР</t>
+  </si>
+  <si>
+    <t>Новый анализ с БД</t>
+  </si>
+  <si>
+    <t>MTA_SKYNET</t>
+  </si>
+  <si>
+    <t>Пробойный бот со сменщаемым стопом</t>
   </si>
 </sst>
 </file>
@@ -91,7 +155,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -99,15 +163,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -619,4 +707,371 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67D0C1B4-2C76-4C34-9797-70BE6724B2A0}">
+  <dimension ref="A2:J25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="10" width="26.5703125" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>12</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>17</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>18</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>19</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>20</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>21</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>22</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/RoadMap.xlsx
+++ b/RoadMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FAED4B-EBF9-4A11-A641-9E22B52D3D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5ADE21C-B919-4195-9820-D9542203B91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Задачи" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Загрузка данных в виде DirHalfBars</t>
   </si>
@@ -126,6 +126,15 @@
   </si>
   <si>
     <t>Пробойный бот со сменщаемым стопом</t>
+  </si>
+  <si>
+    <t>Канал Бигбара</t>
+  </si>
+  <si>
+    <t>Volume Profile</t>
+  </si>
+  <si>
+    <t>Сбор ликвидности</t>
   </si>
 </sst>
 </file>
@@ -781,7 +790,9 @@
       <c r="B4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
@@ -805,7 +816,6 @@
       <c r="D5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -817,7 +827,9 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>33</v>
+      </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -830,7 +842,9 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4" t="s">
+        <v>34</v>
+      </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>

--- a/RoadMap.xlsx
+++ b/RoadMap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5ADE21C-B919-4195-9820-D9542203B91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0703F9BC-4E1A-4CCA-B8BE-2D3C6F82D133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -774,12 +774,12 @@
       <c r="F3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="7" t="s">
         <v>27</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="7" t="s">
         <v>30</v>
       </c>
     </row>

--- a/RoadMap.xlsx
+++ b/RoadMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0703F9BC-4E1A-4CCA-B8BE-2D3C6F82D133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29055D71-1B17-400C-B24F-09C3854E97D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Задачи" sheetId="1" r:id="rId1"/>
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -205,6 +205,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -759,7 +762,7 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -803,7 +806,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="8" t="s">
         <v>31</v>
       </c>
     </row>

--- a/RoadMap.xlsx
+++ b/RoadMap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29055D71-1B17-400C-B24F-09C3854E97D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7693EE-6EAA-4DE5-9953-064B65ECA2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -150,7 +150,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -160,6 +160,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -185,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -208,6 +214,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -796,7 +805,7 @@
       <c r="C4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="9" t="s">
         <v>22</v>
       </c>
       <c r="E4" s="4" t="s">

--- a/RoadMap.xlsx
+++ b/RoadMap.xlsx
@@ -8,26 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F7693EE-6EAA-4DE5-9953-064B65ECA2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC54BDF-3F3D-479A-8CAD-4B89F449D88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Задачи" sheetId="1" r:id="rId1"/>
     <sheet name="Идеи" sheetId="2" r:id="rId2"/>
     <sheet name="ЗИК" sheetId="3" r:id="rId3"/>
+    <sheet name="стратегии" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="155">
   <si>
     <t>Загрузка данных в виде DirHalfBars</t>
   </si>
@@ -135,6 +145,363 @@
   </si>
   <si>
     <t>Сбор ликвидности</t>
+  </si>
+  <si>
+    <t>Название</t>
+  </si>
+  <si>
+    <t>Плюсы</t>
+  </si>
+  <si>
+    <t>Минусы</t>
+  </si>
+  <si>
+    <t>Идеи</t>
+  </si>
+  <si>
+    <t>Номер</t>
+  </si>
+  <si>
+    <t>1_STAML2_NEWAVE_5_5_0.5_30</t>
+  </si>
+  <si>
+    <t>попробовать сделать направленную версию</t>
+  </si>
+  <si>
+    <t>1_PTA2_LISICA_7_2</t>
+  </si>
+  <si>
+    <t>Б П</t>
+  </si>
+  <si>
+    <t>КТ</t>
+  </si>
+  <si>
+    <t>КТ,теряет выходы</t>
+  </si>
+  <si>
+    <t>1_PTA4_WDDCr_6_30</t>
+  </si>
+  <si>
+    <t>1_PTA4_WDDCrE_6_30</t>
+  </si>
+  <si>
+    <t>КТ,ранние выходы</t>
+  </si>
+  <si>
+    <t>1_PTA10_WIZARD_50_55_12_10_30</t>
+  </si>
+  <si>
+    <t>Статистика</t>
+  </si>
+  <si>
+    <t>Очень странные входы и выходы</t>
+  </si>
+  <si>
+    <t>выкинуть его нафиг, добавить стоп</t>
+  </si>
+  <si>
+    <t>1_PTA11_KUSURUKEN_50_3_20_10_c</t>
+  </si>
+  <si>
+    <t>изучить логику, добавиьб стоп</t>
+  </si>
+  <si>
+    <t>1_PTA12_SWDDCr_10_40_0.25_5_5</t>
+  </si>
+  <si>
+    <t>стопы</t>
+  </si>
+  <si>
+    <t>Адаптивный стоп</t>
+  </si>
+  <si>
+    <t>ШБ, КТ, часто стопит в хаях,теряет выходы</t>
+  </si>
+  <si>
+    <t>1_PTA14_RWDDCr_15_30_35_45</t>
+  </si>
+  <si>
+    <t>Улучшить определение боковика</t>
+  </si>
+  <si>
+    <t>Иногда занимал топ</t>
+  </si>
+  <si>
+    <t>1_PTA15_KERRIGAN_5</t>
+  </si>
+  <si>
+    <t>Частые стопы, УБ, КТ,ранние выходы</t>
+  </si>
+  <si>
+    <t>1_PTA15_WIDOWMAKER_5_30</t>
+  </si>
+  <si>
+    <t>ШБ</t>
+  </si>
+  <si>
+    <t>1_STAML2_CHAOS_60_2_30</t>
+  </si>
+  <si>
+    <t>Смена тренда, Сильные тренды</t>
+  </si>
+  <si>
+    <t>Стабильный тренд (СТ) П</t>
+  </si>
+  <si>
+    <t>Восприятие</t>
+  </si>
+  <si>
+    <t>Перспективы</t>
+  </si>
+  <si>
+    <t>Общий</t>
+  </si>
+  <si>
+    <t>1_PTA2_BVGFIX_7_1_1</t>
+  </si>
+  <si>
+    <t>СТ</t>
+  </si>
+  <si>
+    <t>СТ, ШБ</t>
+  </si>
+  <si>
+    <t>1_PTA2_BDDC_FIX_20_1_1</t>
+  </si>
+  <si>
+    <t>1_PTA2_BBBU_14_1_1</t>
+  </si>
+  <si>
+    <t>1_PTA2_BBBUr_7_1_1</t>
+  </si>
+  <si>
+    <t>1_PTA15_TRACER_10_0</t>
+  </si>
+  <si>
+    <t>КТ, УБ, РВ</t>
+  </si>
+  <si>
+    <t>1_PTA2_DDCrWork_5</t>
+  </si>
+  <si>
+    <t>КТ, ШБ, РВ</t>
+  </si>
+  <si>
+    <t>1_LTA_OKROSHKA_10_80</t>
+  </si>
+  <si>
+    <t>1_LTA_PIN_10_6_40_5</t>
+  </si>
+  <si>
+    <t>1_OGTA4_DOG_10_40</t>
+  </si>
+  <si>
+    <t>1_PTA10_MAGIC_40_80_3</t>
+  </si>
+  <si>
+    <t>хз…</t>
+  </si>
+  <si>
+    <t>все</t>
+  </si>
+  <si>
+    <t>удалить и забыть про него</t>
+  </si>
+  <si>
+    <t>1_PTA10_SORCERER_90_10_3_30_15_20</t>
+  </si>
+  <si>
+    <t>трэш…</t>
+  </si>
+  <si>
+    <t>1_PTA13_DWDDCr_70_40_10</t>
+  </si>
+  <si>
+    <t>П</t>
+  </si>
+  <si>
+    <t>Почти все</t>
+  </si>
+  <si>
+    <t>1_STAML2_GOLDENMEAN_60_2_30_30</t>
+  </si>
+  <si>
+    <t>редкие сделки</t>
+  </si>
+  <si>
+    <t>Подумать над возможностью увеличения кс</t>
+  </si>
+  <si>
+    <t>1_PTA15_SILVANA_5_30_5</t>
+  </si>
+  <si>
+    <t>КТ Б</t>
+  </si>
+  <si>
+    <t>1_PTA15_VALLA_10_0</t>
+  </si>
+  <si>
+    <t>ШБ Б П</t>
+  </si>
+  <si>
+    <t>стоп попробовать</t>
+  </si>
+  <si>
+    <t>1_PTA15_ANNA_5_30</t>
+  </si>
+  <si>
+    <t>1_PTA2_BDDCr_UNIVERSAL_7_1_1</t>
+  </si>
+  <si>
+    <t>5_PTA8_LOBSTER_10_2</t>
+  </si>
+  <si>
+    <t>5_PTA8_OBBY_10_1</t>
+  </si>
+  <si>
+    <t>СТ, есть прям GT</t>
+  </si>
+  <si>
+    <t>СТ, П</t>
+  </si>
+  <si>
+    <t>Б, КТ</t>
+  </si>
+  <si>
+    <t>1_STA2_100_3_25</t>
+  </si>
+  <si>
+    <t>П, СТ</t>
+  </si>
+  <si>
+    <t>СмТ, КТ</t>
+  </si>
+  <si>
+    <t>1_STA2_FAST_100_3_20_25</t>
+  </si>
+  <si>
+    <t>1_STA2_SLOW_100_5_15_25</t>
+  </si>
+  <si>
+    <t>СмТ, КТ, СложВыход</t>
+  </si>
+  <si>
+    <t>1_STA2_ULTRA_100_3_20_15</t>
+  </si>
+  <si>
+    <t>1_PTA18_ARTAS_100_3_10_20</t>
+  </si>
+  <si>
+    <t>CмТ, странности со стопами (не всегда срабатывает)</t>
+  </si>
+  <si>
+    <t>1_PTA18_KELTHUZAD_100_3_10_10</t>
+  </si>
+  <si>
+    <t>CмТ, странности</t>
+  </si>
+  <si>
+    <t>1_PTA18_CHOGALL_100_7_10_40</t>
+  </si>
+  <si>
+    <t>Поискать баги</t>
+  </si>
+  <si>
+    <t>1_PTA18_GULDAN_100_7_10_40</t>
+  </si>
+  <si>
+    <t>CмТ, странности, быстрый ход</t>
+  </si>
+  <si>
+    <t>1_PTA18_DIABLO_100_5_15_30</t>
+  </si>
+  <si>
+    <t>1_PTA18_DEHAKA_100_5_15_30</t>
+  </si>
+  <si>
+    <t>1_PTA18_REXXAR_100_5_10_50_30</t>
+  </si>
+  <si>
+    <t>1_PTA18_VARIAN_100_3_10_20_25</t>
+  </si>
+  <si>
+    <t>1_LTA2_LOGAN_10_100_30</t>
+  </si>
+  <si>
+    <t>Б</t>
+  </si>
+  <si>
+    <t>1_PTA18_BLAZE_70_10_71_40_30_0</t>
+  </si>
+  <si>
+    <t>чет очень wizard напоминает, КТ</t>
+  </si>
+  <si>
+    <t>1_PTA18_BLAZE_70_10_71_40_30_1</t>
+  </si>
+  <si>
+    <t>Выглядит лучше, чем собрат без стопа</t>
+  </si>
+  <si>
+    <t>странности</t>
+  </si>
+  <si>
+    <t>1_PTA19_ANUBARAK_30_10_40_20_10_0</t>
+  </si>
+  <si>
+    <t>Выглядит лучше, чем BLAZE</t>
+  </si>
+  <si>
+    <t>1_PTA19_ANUBARAK_30_10_40_20_10_1</t>
+  </si>
+  <si>
+    <t>хз..</t>
+  </si>
+  <si>
+    <t>ШБ, странности, стоп в хаях ШБ</t>
+  </si>
+  <si>
+    <t>1_PTA19_JOHANNA_100_7_10_10_40_20_0</t>
+  </si>
+  <si>
+    <t>1_PTA19_JOHANNA_100_7_10_10_40_20_1</t>
+  </si>
+  <si>
+    <t>1_PTA19_TYRAEL_100_10_5_10_50_40_0</t>
+  </si>
+  <si>
+    <t>1_PTA19_TYRAEL_100_10_5_10_50_40_1</t>
+  </si>
+  <si>
+    <t>Стоп по типу баров. На импульс</t>
+  </si>
+  <si>
+    <t>СтатистикаF</t>
+  </si>
+  <si>
+    <t>СтатистикаS</t>
+  </si>
+  <si>
+    <t>ОбщФ</t>
+  </si>
+  <si>
+    <t>ОбщС</t>
+  </si>
+  <si>
+    <t>У</t>
+  </si>
+  <si>
+    <t>БТ,У</t>
+  </si>
+  <si>
+    <t>СмТ, долгий стоп, стоп не всегда спасает</t>
+  </si>
+  <si>
+    <t>СмТ, Плоский тренд, ШБ, стоп не всегда спасает</t>
+  </si>
+  <si>
+    <t>СмТ, Плоский тренд</t>
   </si>
 </sst>
 </file>
@@ -557,7 +924,7 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -783,7 +1150,7 @@
       <c r="E3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G3" s="7" t="s">
@@ -839,7 +1206,7 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="4"/>
@@ -1100,4 +1467,1969 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31D2D605-E51B-4389-B345-910A8DB80FC7}">
+  <dimension ref="A1:L841"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="3"/>
+    <col min="2" max="2" width="38.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="49.28515625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="45.42578125" style="3" customWidth="1"/>
+    <col min="6" max="9" width="13.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>9</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>9</v>
+      </c>
+      <c r="J2">
+        <f>SUM(F2:I2)</f>
+        <v>25</v>
+      </c>
+      <c r="K2">
+        <f>J2-H2</f>
+        <v>25</v>
+      </c>
+      <c r="L2">
+        <f>J2-G2</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3">
+        <v>6</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J52" si="0">SUM(F3:I3)</f>
+        <v>21</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K52" si="1">J3-H3</f>
+        <v>16</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L52" si="2">J3-G3</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>8</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>9</v>
+      </c>
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="G8">
+        <v>7</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>6</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>5</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11">
+        <v>7</v>
+      </c>
+      <c r="G11">
+        <v>8</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>5</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12">
+        <v>7</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>9</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13">
+        <v>4</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>5</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>5</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16">
+        <v>4</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16">
+        <v>6</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17">
+        <v>6</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
+      <c r="I17">
+        <v>5</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18">
+        <v>8</v>
+      </c>
+      <c r="H18">
+        <v>6</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19">
+        <v>3</v>
+      </c>
+      <c r="G19">
+        <v>7</v>
+      </c>
+      <c r="H19">
+        <v>7</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <v>7</v>
+      </c>
+      <c r="H20">
+        <v>7</v>
+      </c>
+      <c r="I20">
+        <v>4</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21">
+        <v>7</v>
+      </c>
+      <c r="G21">
+        <v>9</v>
+      </c>
+      <c r="H21">
+        <v>7</v>
+      </c>
+      <c r="I21">
+        <v>5</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>4</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>5</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>4</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>8</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F25">
+        <v>6</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+      <c r="H25">
+        <v>5</v>
+      </c>
+      <c r="I25">
+        <v>7</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26">
+        <v>7</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+      <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26">
+        <v>6</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F27">
+        <v>7</v>
+      </c>
+      <c r="G27">
+        <v>8</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>7</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B28" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28">
+        <v>6</v>
+      </c>
+      <c r="G28">
+        <v>7</v>
+      </c>
+      <c r="H28">
+        <v>7</v>
+      </c>
+      <c r="I28">
+        <v>5</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29">
+        <v>4</v>
+      </c>
+      <c r="H29">
+        <v>4</v>
+      </c>
+      <c r="I29">
+        <v>5</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B30" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30">
+        <v>4</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>4</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>6</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F32">
+        <v>6</v>
+      </c>
+      <c r="G32">
+        <v>2</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>5</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B33" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F33">
+        <v>7</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+      <c r="H33">
+        <v>3</v>
+      </c>
+      <c r="I33">
+        <v>7</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B34" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F34">
+        <v>7</v>
+      </c>
+      <c r="G34">
+        <v>5</v>
+      </c>
+      <c r="H34">
+        <v>3</v>
+      </c>
+      <c r="I34">
+        <v>7</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B35" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F35">
+        <v>5</v>
+      </c>
+      <c r="G35">
+        <v>2</v>
+      </c>
+      <c r="H35">
+        <v>4</v>
+      </c>
+      <c r="I35">
+        <v>5</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F36">
+        <v>8</v>
+      </c>
+      <c r="G36">
+        <v>7</v>
+      </c>
+      <c r="H36">
+        <v>6</v>
+      </c>
+      <c r="I36">
+        <v>8</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B37" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F37">
+        <v>7</v>
+      </c>
+      <c r="G37">
+        <v>6</v>
+      </c>
+      <c r="H37">
+        <v>6</v>
+      </c>
+      <c r="I37">
+        <v>7</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F38">
+        <v>7</v>
+      </c>
+      <c r="G38">
+        <v>6</v>
+      </c>
+      <c r="H38">
+        <v>7</v>
+      </c>
+      <c r="I38">
+        <v>8</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B39" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F39">
+        <v>6</v>
+      </c>
+      <c r="G39">
+        <v>5</v>
+      </c>
+      <c r="H39">
+        <v>7</v>
+      </c>
+      <c r="I39">
+        <v>7</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B40" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F40">
+        <v>7</v>
+      </c>
+      <c r="G40">
+        <v>6</v>
+      </c>
+      <c r="H40">
+        <v>7</v>
+      </c>
+      <c r="I40">
+        <v>8</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B41" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F41">
+        <v>7</v>
+      </c>
+      <c r="G41">
+        <v>6</v>
+      </c>
+      <c r="H41">
+        <v>7</v>
+      </c>
+      <c r="I41">
+        <v>8</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="L41">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B42" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F42">
+        <v>9</v>
+      </c>
+      <c r="G42">
+        <v>7</v>
+      </c>
+      <c r="H42">
+        <v>6</v>
+      </c>
+      <c r="I42">
+        <v>8</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B43" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F43">
+        <v>8</v>
+      </c>
+      <c r="G43">
+        <v>6</v>
+      </c>
+      <c r="H43">
+        <v>6</v>
+      </c>
+      <c r="I43">
+        <v>8</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B44" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44">
+        <v>5</v>
+      </c>
+      <c r="G44">
+        <v>7</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>4</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B45" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F45">
+        <v>6</v>
+      </c>
+      <c r="G45">
+        <v>7</v>
+      </c>
+      <c r="H45">
+        <v>7</v>
+      </c>
+      <c r="I45">
+        <v>5</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B46" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F46">
+        <v>7</v>
+      </c>
+      <c r="G46">
+        <v>3</v>
+      </c>
+      <c r="H46">
+        <v>6</v>
+      </c>
+      <c r="I46">
+        <v>6</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B47" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F47">
+        <v>7</v>
+      </c>
+      <c r="G47">
+        <v>5</v>
+      </c>
+      <c r="H47">
+        <v>7</v>
+      </c>
+      <c r="I47">
+        <v>6</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="L47">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B48" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F48">
+        <v>6</v>
+      </c>
+      <c r="G48">
+        <v>4</v>
+      </c>
+      <c r="H48">
+        <v>5</v>
+      </c>
+      <c r="I48">
+        <v>6</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="K48">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="L48">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B49" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F49">
+        <v>10</v>
+      </c>
+      <c r="G49">
+        <v>9</v>
+      </c>
+      <c r="H49">
+        <v>7</v>
+      </c>
+      <c r="I49">
+        <v>10</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="K49">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="L49">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B50" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F50">
+        <v>11</v>
+      </c>
+      <c r="G50">
+        <v>8</v>
+      </c>
+      <c r="H50">
+        <v>6</v>
+      </c>
+      <c r="I50">
+        <v>11</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B51" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F51">
+        <v>9</v>
+      </c>
+      <c r="G51">
+        <v>6</v>
+      </c>
+      <c r="H51">
+        <v>7</v>
+      </c>
+      <c r="I51">
+        <v>9</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="L51">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B52" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F52">
+        <v>10</v>
+      </c>
+      <c r="G52">
+        <v>6</v>
+      </c>
+      <c r="H52">
+        <v>7</v>
+      </c>
+      <c r="I52">
+        <v>10</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="L52">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="836" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A836" s="3">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="837" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A837" s="3">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="838" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A838" s="3">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="839" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A839" s="3">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="840" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A840" s="3">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="841" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A841" s="3">
+        <v>841</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="J1:J1048576 K1:L1">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:K1048576">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L1:L1048576">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/RoadMap.xlsx
+++ b/RoadMap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC54BDF-3F3D-479A-8CAD-4B89F449D88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E06443-B80E-449A-9EBE-99F0D395B1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2334,22 +2334,22 @@
         <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I24">
         <v>8</v>
       </c>
       <c r="J24">
         <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="K24">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
       <c r="L24">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.25">

--- a/RoadMap.xlsx
+++ b/RoadMap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\exchange\RichLaughter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E06443-B80E-449A-9EBE-99F0D395B1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC3DBA7-B389-404C-8523-58174E0B4181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1521,6 +1521,9 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
       <c r="B2" s="4" t="s">
         <v>41</v>
       </c>
@@ -1559,6 +1562,9 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
       <c r="B3" s="3" t="s">
         <v>43</v>
       </c>
@@ -1594,6 +1600,9 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
       <c r="B4" s="3" t="s">
         <v>47</v>
       </c>
@@ -1629,6 +1638,9 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
       <c r="B5" s="3" t="s">
         <v>48</v>
       </c>
@@ -1664,6 +1676,9 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
       <c r="B6" s="3" t="s">
         <v>50</v>
       </c>
@@ -1702,6 +1717,9 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
       <c r="B7" s="3" t="s">
         <v>54</v>
       </c>
@@ -1740,6 +1758,9 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
       <c r="B8" s="3" t="s">
         <v>56</v>
       </c>
@@ -1778,6 +1799,9 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
       <c r="B9" s="3" t="s">
         <v>60</v>
       </c>
@@ -1816,6 +1840,9 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
       <c r="B10" s="3" t="s">
         <v>63</v>
       </c>
@@ -1851,6 +1878,9 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
       <c r="B11" s="3" t="s">
         <v>65</v>
       </c>
@@ -1886,6 +1916,9 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
       <c r="B12" s="3" t="s">
         <v>67</v>
       </c>
@@ -1924,6 +1957,9 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
       <c r="B13" s="3" t="s">
         <v>73</v>
       </c>
@@ -1959,6 +1995,9 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
       <c r="B14" s="3" t="s">
         <v>76</v>
       </c>
@@ -1994,6 +2033,9 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
       <c r="B15" s="3" t="s">
         <v>77</v>
       </c>
@@ -2029,6 +2071,9 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
       <c r="B16" s="3" t="s">
         <v>78</v>
       </c>
@@ -2063,7 +2108,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
       <c r="B17" s="3" t="s">
         <v>79</v>
       </c>
@@ -2098,7 +2146,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
       <c r="B18" s="3" t="s">
         <v>81</v>
       </c>
@@ -2133,7 +2184,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
       <c r="B19" s="3" t="s">
         <v>83</v>
       </c>
@@ -2168,7 +2222,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
       <c r="B20" s="3" t="s">
         <v>84</v>
       </c>
@@ -2203,7 +2260,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
       <c r="B21" s="3" t="s">
         <v>85</v>
       </c>
@@ -2238,7 +2298,10 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
       <c r="B22" s="3" t="s">
         <v>86</v>
       </c>
@@ -2276,7 +2339,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
       <c r="B23" s="3" t="s">
         <v>90</v>
       </c>
@@ -2314,7 +2380,10 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
       <c r="B24" s="3" t="s">
         <v>92</v>
       </c>
@@ -2352,7 +2421,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
       <c r="B25" s="3" t="s">
         <v>95</v>
       </c>
@@ -2390,7 +2462,10 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
       <c r="B26" s="3" t="s">
         <v>98</v>
       </c>
@@ -2425,7 +2500,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
       <c r="B27" s="3" t="s">
         <v>100</v>
       </c>
@@ -2463,7 +2541,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
       <c r="B28" s="3" t="s">
         <v>103</v>
       </c>
@@ -2498,7 +2579,10 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
       <c r="B29" s="3" t="s">
         <v>104</v>
       </c>
@@ -2533,7 +2617,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
       <c r="B30" s="3" t="s">
         <v>105</v>
       </c>
@@ -2568,7 +2655,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
       <c r="B31" s="3" t="s">
         <v>106</v>
       </c>
@@ -2603,7 +2693,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
       <c r="B32" s="3" t="s">
         <v>110</v>
       </c>
@@ -2638,7 +2731,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
       <c r="B33" s="3" t="s">
         <v>113</v>
       </c>
@@ -2673,7 +2769,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
       <c r="B34" s="3" t="s">
         <v>114</v>
       </c>
@@ -2708,7 +2807,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
       <c r="B35" s="3" t="s">
         <v>116</v>
       </c>
@@ -2743,7 +2845,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
       <c r="B36" s="3" t="s">
         <v>117</v>
       </c>
@@ -2781,7 +2886,10 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
       <c r="B37" s="3" t="s">
         <v>119</v>
       </c>
@@ -2819,7 +2927,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
       <c r="B38" s="3" t="s">
         <v>121</v>
       </c>
@@ -2857,7 +2968,10 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
       <c r="B39" s="3" t="s">
         <v>123</v>
       </c>
@@ -2892,7 +3006,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
       <c r="B40" s="3" t="s">
         <v>125</v>
       </c>
@@ -2930,7 +3047,10 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
       <c r="B41" s="3" t="s">
         <v>126</v>
       </c>
@@ -2968,7 +3088,10 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
       <c r="B42" s="3" t="s">
         <v>127</v>
       </c>
@@ -3006,7 +3129,10 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
       <c r="B43" s="3" t="s">
         <v>128</v>
       </c>
@@ -3044,7 +3170,10 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
+        <v>43</v>
+      </c>
       <c r="B44" s="3" t="s">
         <v>129</v>
       </c>
@@ -3079,7 +3208,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <v>44</v>
+      </c>
       <c r="B45" s="3" t="s">
         <v>131</v>
       </c>
@@ -3114,7 +3246,10 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
       <c r="B46" s="3" t="s">
         <v>133</v>
       </c>
@@ -3149,7 +3284,10 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
+        <v>46</v>
+      </c>
       <c r="B47" s="3" t="s">
         <v>136</v>
       </c>
@@ -3184,7 +3322,10 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
       <c r="B48" s="3" t="s">
         <v>138</v>
       </c>
@@ -3219,7 +3360,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
       <c r="B49" s="3" t="s">
         <v>141</v>
       </c>
@@ -3254,7 +3398,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
       <c r="B50" s="3" t="s">
         <v>142</v>
       </c>
@@ -3289,7 +3436,10 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
       <c r="B51" s="3" t="s">
         <v>143</v>
       </c>
@@ -3324,7 +3474,10 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
       <c r="B52" s="3" t="s">
         <v>144</v>
       </c>
